--- a/зыуз2.xlsx
+++ b/зыуз2.xlsx
@@ -75,7 +75,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,13 +93,21 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -109,6 +117,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -140,32 +154,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -449,150 +465,150 @@
   <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="6" t="s">
+      <c r="G1" s="11"/>
+      <c r="H1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="7">
         <v>45000</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="6">
         <v>5</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="6">
         <v>5</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="7">
         <v>225000</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="7">
         <v>213750</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="10">
+      <c r="G2" s="4"/>
+      <c r="H2" s="8">
         <v>0.2</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="5">
         <v>45000</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="7">
         <v>18000</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="6">
         <v>10</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="6">
         <v>3</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="7">
         <v>180000</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="7">
         <v>174600</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="7">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="5">
         <v>36000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="7">
         <v>1500</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="6">
         <v>25</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="6">
         <v>10</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="7">
         <v>37500</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="7">
         <v>33750</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="7">
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="5">
         <v>7500</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="7">
         <v>800</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="6">
         <v>30</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="6">
         <v>7</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="7">
         <v>24000</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="7">
         <v>22320</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="7">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="5">
         <v>4800</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="10">
         <f>SUM(B2:B5)</f>
         <v>65300</v>
       </c>
